--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,244 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127318789</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stutgöl A21658, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>568450</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6433175</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127318748</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stutgöl A21658, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>568450</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433175</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127318606</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127318789</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>127318748</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127318606</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127318789</v>
       </c>
       <c r="B3" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>127318748</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127318606</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127318789</v>
       </c>
       <c r="B3" t="n">
-        <v>57676</v>
+        <v>57679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>127318748</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127318606</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127318789</v>
       </c>
       <c r="B3" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>127318748</v>
       </c>
       <c r="B4" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127318606</v>
+        <v>127318789</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,14 +708,17 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stutgöl A21658, Stutgöl A21658, Sm</t>
+          <t>Stutgöl A21658, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127318789</v>
+        <v>127318748</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,125 +910,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>127318748</v>
-      </c>
-      <c r="B4" t="n">
-        <v>58042</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Stutgöl A21658, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>568450</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6433175</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Björn Stenberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Björn Stenberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127318789</v>
+        <v>127318606</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,17 +708,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stutgöl A21658, Sm</t>
+          <t>Stutgöl A21658, Stutgöl A21658, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127318748</v>
+        <v>127318789</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -876,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +907,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127318748</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58042</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stutgöl A21658, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>568450</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433175</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21658-2025 artfynd.xlsx
+++ b/artfynd/A 21658-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127318606</v>
+        <v>127318789</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,14 +708,17 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stutgöl A21658, Stutgöl A21658, Sm</t>
+          <t>Stutgöl A21658, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127318789</v>
+        <v>127318748</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,32 +913,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127318748</v>
+        <v>127318606</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,17 +946,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stutgöl A21658, Sm</t>
+          <t>Stutgöl A21658, Stutgöl A21658, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
